--- a/เอกสารและรายชื่อคณะสีแสด_ปี69/ใบเช็คชื่อ/ไฟล์Excel/04_ใบเช็คชื่อ_ฝ่ายเชียร์ลีดเดอร์_คณะสีแสด_ปี69.xlsx
+++ b/เอกสารและรายชื่อคณะสีแสด_ปี69/ใบเช็คชื่อ/ไฟล์Excel/04_ใบเช็คชื่อ_ฝ่ายเชียร์ลีดเดอร์_คณะสีแสด_ปี69.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="98">
   <si>
-    <t>ใบรายชื่อฝ่ายเชียร์ลีดเดอร์ คณะสีแสด ปี 2569</t>
+    <t>ใบเช็คชื่อฝ่ายเชียร์ลีดเดอร์ คณะสีแสด ปี 2569</t>
   </si>
   <si>
     <t>ลำดับ</t>
